--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-13.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-13.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/metodos_aprovados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="11_643D508254DA3C2617B82211595ED87656CD1538" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2ECEE546-73CD-4303-9213-E6B36D0AF146}"/>
+  <xr:revisionPtr revIDLastSave="34" documentId="11_643D508254DA3C2617B82211595ED87656CD1538" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A708DD0-4150-472B-9131-A7F6C6655D53}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="204">
   <si>
     <t>Data</t>
   </si>
@@ -629,6 +629,9 @@
   </si>
   <si>
     <t>1x3</t>
+  </si>
+  <si>
+    <t>1X2</t>
   </si>
 </sst>
 </file>
@@ -704,6 +707,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2641,7 +2648,7 @@
         <v>100</v>
       </c>
       <c r="N33" t="s">
-        <v>27</v>
+        <v>203</v>
       </c>
       <c r="O33" t="s">
         <v>28</v>
@@ -2691,7 +2698,7 @@
         <v>100</v>
       </c>
       <c r="N34" t="s">
-        <v>27</v>
+        <v>203</v>
       </c>
       <c r="O34" t="s">
         <v>28</v>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-13.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-13.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U36"/>
+  <dimension ref="A1:W39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,6 +534,16 @@
           <t>status</t>
         </is>
       </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>PnL_u</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>PnL_R$</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -613,6 +623,8 @@
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -692,6 +704,8 @@
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -771,6 +785,8 @@
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -850,6 +866,8 @@
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -929,6 +947,8 @@
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1008,6 +1028,8 @@
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1087,6 +1109,8 @@
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1166,6 +1190,8 @@
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1245,6 +1271,8 @@
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1324,6 +1352,8 @@
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1403,6 +1433,8 @@
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1482,6 +1514,8 @@
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1561,6 +1595,8 @@
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1640,6 +1676,8 @@
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1757,8 @@
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1798,6 +1838,8 @@
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1807,37 +1849,37 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SERBIA 1</t>
+          <t>SPAIN 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>FK IMT Novi Beograd x Crvena Zvezda</t>
+          <t>Mallorca x Sabadell</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FK IMT Novi Beograd</t>
+          <t>Mallorca</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Crvena Zvezda</t>
+          <t>Sabadell</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay 3x0 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Correct Score (3x0)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1846,20 +1888,20 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>7.2</v>
+        <v>22</v>
       </c>
       <c r="K18" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>16.13</v>
+        <v>9.52</v>
       </c>
       <c r="M18" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>0x1</t>
+          <t>vs</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1874,9 +1916,17 @@
           <t>⏳ PENDENTE</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr"/>
+      <c r="S18" t="n">
+        <v>9.19</v>
+      </c>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1891,22 +1941,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TURKEY 1</t>
+          <t>SERBIA 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Galatasaray x Kocaelispor</t>
+          <t>FK IMT Novi Beograd x Crvena Zvezda</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>FK IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Crvena Zvezda</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1925,20 +1975,20 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="K19" t="n">
         <v>1.31</v>
       </c>
       <c r="L19" t="n">
-        <v>18.52</v>
+        <v>16.13</v>
       </c>
       <c r="M19" t="n">
         <v>100</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>1x0</t>
+          <t>0x1</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -1956,6 +2006,8 @@
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1965,37 +2017,37 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>BELGIUM 1</t>
+          <t>TURKEY 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>RAAL La Louviere x Kortrijk</t>
+          <t>Galatasaray x Kocaelispor</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAAL La Louviere</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kortrijk</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lay 2x2 Top 3 (Aprovado)</t>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Correct Score (2x2)</t>
+          <t>Match Odds (Draw)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2004,20 +2056,20 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>17</v>
+        <v>6.4</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="L20" t="n">
-        <v>6.25</v>
+        <v>18.52</v>
       </c>
       <c r="M20" t="n">
         <v>100</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>3x0</t>
+          <t>1x0</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2035,6 +2087,8 @@
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2044,37 +2098,37 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ROMANIA 1</t>
+          <t>BELGIUM 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>FC Hunedoara x Universitatea Craiova</t>
+          <t>RAAL La Louviere x Kortrijk</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FC Hunedoara</t>
+          <t>RAAL La Louviere</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Universitatea Craiova</t>
+          <t>Kortrijk</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lay 0x3 Top 3 (Aprovado)</t>
+          <t>Lay 2x2 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Correct Score (0x3)</t>
+          <t>Correct Score (2x2)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2083,20 +2137,20 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>4.76</v>
+        <v>6.25</v>
       </c>
       <c r="M21" t="n">
         <v>100</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0x1</t>
+          <t>3x0</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2114,6 +2168,8 @@
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2128,32 +2184,32 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ISRAEL 1</t>
+          <t>ROMANIA 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Hapoel Petach Tikva x Hapoel Be'er Sheva</t>
+          <t>FC Hunedoara x Universitatea Craiova</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hapoel Petach Tikva</t>
+          <t>FC Hunedoara</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Universitatea Craiova</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
+          <t>Lay 0x3 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Match Odds (Home)</t>
+          <t>Correct Score (0x3)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2162,20 +2218,20 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="K22" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>16.67</v>
+        <v>4.76</v>
       </c>
       <c r="M22" t="n">
         <v>100</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0x2</t>
+          <t>0x1</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2193,6 +2249,8 @@
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2202,37 +2260,37 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ARGENTINA 1</t>
+          <t>ISRAEL 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Tigre x Rosario Central</t>
+          <t>Hapoel Petach Tikva x Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tigre</t>
+          <t>Hapoel Petach Tikva</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lay Over 4.5 FT (Under Pesado)</t>
+          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Over 4.5 FT</t>
+          <t>Match Odds (Home)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2241,20 +2299,20 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="K23" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="L23" t="n">
-        <v>5.56</v>
+        <v>16.67</v>
       </c>
       <c r="M23" t="n">
         <v>100</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0x1</t>
+          <t>0x2</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2272,6 +2330,8 @@
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2281,37 +2341,37 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CROATIA 1</t>
+          <t>ARGENTINA 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Hajduk Split x Slaven Belupo</t>
+          <t>Tigre x Rosario Central</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Tigre</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Slaven Belupo</t>
+          <t>Rosario Central</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay Over 4.5 FT (Under Pesado)</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Over 4.5 FT</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2320,20 +2380,20 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="K24" t="n">
-        <v>1.31</v>
+        <v>1.49</v>
       </c>
       <c r="L24" t="n">
-        <v>16.67</v>
+        <v>5.56</v>
       </c>
       <c r="M24" t="n">
         <v>100</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>1x0</t>
+          <t>0x1</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2351,6 +2411,8 @@
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2365,22 +2427,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>NETHERLANDS 1</t>
+          <t>CROATIA 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>PSV x Sparta Rotterdam</t>
+          <t>Hajduk Split x Slaven Belupo</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Slaven Belupo</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2399,20 +2461,20 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>9.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="K25" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="L25" t="n">
-        <v>11.36</v>
+        <v>16.67</v>
       </c>
       <c r="M25" t="n">
         <v>100</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>4x1</t>
+          <t>1x0</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2430,6 +2492,8 @@
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2439,27 +2503,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>GREECE 1</t>
+          <t>NETHERLANDS 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Panathinaikos x Panaitolikos</t>
+          <t>PSV x Sparta Rotterdam</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2478,20 +2542,20 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="L26" t="n">
-        <v>16.67</v>
+        <v>11.36</v>
       </c>
       <c r="M26" t="n">
         <v>100</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>3x0</t>
+          <t>4x1</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2509,6 +2573,8 @@
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2518,27 +2584,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>FRANCE 1</t>
+          <t>GREECE 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Brest x Paris St-G</t>
+          <t>Panathinaikos x Panaitolikos</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Paris St-G</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2557,20 +2623,20 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="K27" t="n">
         <v>1.27</v>
       </c>
       <c r="L27" t="n">
-        <v>15.15</v>
+        <v>16.67</v>
       </c>
       <c r="M27" t="n">
         <v>100</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>0x1</t>
+          <t>3x0</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2588,6 +2654,8 @@
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2597,27 +2665,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>BOLIVIA 1</t>
+          <t>FRANCE 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Always Ready x Guabira</t>
+          <t>Brest x Paris St-G</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Always Ready</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Paris St-G</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2636,20 +2704,20 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="K28" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="L28" t="n">
-        <v>11.11</v>
+        <v>15.15</v>
       </c>
       <c r="M28" t="n">
         <v>100</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>6x0</t>
+          <t>0x1</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2667,6 +2735,8 @@
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2681,32 +2751,32 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>COLOMBIA 1</t>
+          <t>BOLIVIA 1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Deportivo Pereira x Atletico Bucaramanga</t>
+          <t>Always Ready x Guabira</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Deportivo Pereira</t>
+          <t>Always Ready</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Atletico Bucaramanga</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Match Odds (Home)</t>
+          <t>Match Odds (Draw)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2715,20 +2785,20 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="K29" t="n">
-        <v>1.59</v>
+        <v>1.19</v>
       </c>
       <c r="L29" t="n">
-        <v>15.62</v>
+        <v>11.11</v>
       </c>
       <c r="M29" t="n">
         <v>100</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>1x3</t>
+          <t>6x0</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2746,6 +2816,8 @@
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2755,27 +2827,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>PORTUGAL 1</t>
+          <t>COLOMBIA 1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Famalicao x Sporting Lisbon</t>
+          <t>Deportivo Pereira x Atletico Bucaramanga</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Famalicao</t>
+          <t>Deportivo Pereira</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sporting Lisbon</t>
+          <t>Atletico Bucaramanga</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2794,20 +2866,20 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="K30" t="n">
-        <v>1.51</v>
+        <v>1.59</v>
       </c>
       <c r="L30" t="n">
-        <v>14.71</v>
+        <v>15.62</v>
       </c>
       <c r="M30" t="n">
         <v>100</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>1x3</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -2825,6 +2897,8 @@
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2834,37 +2908,37 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>BRAZIL 1</t>
+          <t>PORTUGAL 1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Flamengo x Corinthians</t>
+          <t>Famalicao x Sporting Lisbon</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Famalicao</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Sporting Lisbon</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Match Odds (Home)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2873,20 +2947,20 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="K31" t="n">
-        <v>1.29</v>
+        <v>1.51</v>
       </c>
       <c r="L31" t="n">
-        <v>18.52</v>
+        <v>14.71</v>
       </c>
       <c r="M31" t="n">
         <v>100</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2x1</t>
+          <t>1x1</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -2904,6 +2978,8 @@
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2913,7 +2989,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2923,27 +2999,27 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>CA Independiente x San Lorenzo</t>
+          <t>Argentinos Jrs x Gimnasia L.P.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>CA Independiente</t>
+          <t>Argentinos Jrs</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>San Lorenzo</t>
+          <t>Gimnasia L.P.</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lay Over 4.5 FT (Under Pesado)</t>
+          <t>Lay 3x0 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Over 4.5 FT</t>
+          <t>Correct Score (3x0)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2955,13 +3031,13 @@
         <v>19.5</v>
       </c>
       <c r="K32" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>5.41</v>
+        <v>10.81</v>
       </c>
       <c r="M32" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
@@ -2970,19 +3046,29 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr"/>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>1</v>
+      </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr"/>
+          <t>🟢 GREEN</t>
+        </is>
+      </c>
+      <c r="S32" t="n">
+        <v>10.43</v>
+      </c>
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
+      <c r="V32" t="n">
+        <v>0.0522</v>
+      </c>
+      <c r="W32" t="n">
+        <v>10.43</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2992,37 +3078,37 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>USA 1</t>
+          <t>ARGENTINA 1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps x Austin FC</t>
+          <t>Argentinos Juniors x Gimnasia La Plata</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Argentinos Juniors</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Austin FC</t>
+          <t>Gimnasia La Plata</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay 3x0 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Correct Score (3x0)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3031,20 +3117,20 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>7</v>
+        <v>19.5</v>
       </c>
       <c r="K33" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>16.67</v>
+        <v>10.81</v>
       </c>
       <c r="M33" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>vs</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3059,9 +3145,17 @@
           <t>⏳ PENDENTE</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr"/>
+      <c r="S33" t="n">
+        <v>10.43</v>
+      </c>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3071,37 +3165,37 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>BOLIVIA 1</t>
+          <t>BRAZIL 1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Real Tomayapo x Bolivar</t>
+          <t>Flamengo x Corinthians</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bolivar</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Match Odds (Home)</t>
+          <t>Match Odds (Draw)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3110,20 +3204,20 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="K34" t="n">
-        <v>1.57</v>
+        <v>1.29</v>
       </c>
       <c r="L34" t="n">
-        <v>17.86</v>
+        <v>18.52</v>
       </c>
       <c r="M34" t="n">
         <v>100</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>2x1</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3141,6 +3235,8 @@
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3150,37 +3246,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>22:15</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>COLOMBIA 1</t>
+          <t>BRAZIL 1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Cucuta Deportivo x Millonarios</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Cucuta Deportivo</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Millonarios</t>
-        </is>
-      </c>
+          <t>Flamengo RJ x Corinthians</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lay 0x3 Top 3 (Aprovado)</t>
+          <t>Lay Away Fortaleza 1X (Fav &lt;= 1.40 | O25 &gt;= 1.75)</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Correct Score (0x3)</t>
+          <t>Match Odds (Away)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3189,37 +3277,45 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="L35" t="n">
-        <v>4.76</v>
+        <v>7.14</v>
       </c>
       <c r="M35" t="n">
         <v>100</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>2x1</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr"/>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>1</v>
+      </c>
       <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>⏳ PENDENTE</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>LIQUIDADO</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3229,29 +3325,37 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>BRAZIL 1</t>
+          <t>ARGENTINA 1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Flamengo RJ x Corinthians</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+          <t>CA Independiente x San Lorenzo</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>CA Independiente</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>San Lorenzo</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lay Away Fortaleza 1X (Fav &lt;= 1.40 | O25 &gt;= 1.75)</t>
+          <t>Lay Over 4.5 FT (Under Pesado)</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Match Odds (Away)</t>
+          <t>Over 4.5 FT</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3260,43 +3364,282 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>15</v>
+        <v>19.5</v>
       </c>
       <c r="K36" t="n">
-        <v>1.29</v>
+        <v>1.48</v>
       </c>
       <c r="L36" t="n">
-        <v>7.14</v>
+        <v>5.41</v>
       </c>
       <c r="M36" t="n">
         <v>100</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2x1</t>
+          <t>1x1</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="P36" t="n">
-        <v>1</v>
-      </c>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="n">
-        <v>6.89</v>
-      </c>
-      <c r="T36" t="n">
-        <v>1</v>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>LIQUIDADO</t>
-        </is>
-      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>USA 1</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps x Austin FC</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Austin FC</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Match Odds (Draw)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>7</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L37" t="n">
+        <v>16.67</v>
+      </c>
+      <c r="M37" t="n">
+        <v>100</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>BOLIVIA 1</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Real Tomayapo x Bolivar</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Real Tomayapo</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Bolivar</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Match Odds (Home)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="L38" t="n">
+        <v>17.86</v>
+      </c>
+      <c r="M38" t="n">
+        <v>100</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>22:15</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>COLOMBIA 1</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Cucuta Deportivo x Millonarios</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Cucuta Deportivo</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Millonarios</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Lay 0x3 Top 3 (Aprovado)</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Correct Score (0x3)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>22</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="M39" t="n">
+        <v>100</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-13.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-13.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -605,12 +605,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>4x0</t>
+          <t>4-0</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
@@ -686,12 +686,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>3x1</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
@@ -767,12 +767,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>3x1</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
@@ -848,12 +848,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>3x1</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -929,12 +929,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>8x1</t>
+          <t>8-1</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>5x0</t>
+          <t>5-0</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -1091,12 +1091,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -1172,12 +1172,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2x4</t>
+          <t>2-4</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -1253,12 +1253,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0x0</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P10" t="inlineStr"/>
@@ -1334,12 +1334,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0x7</t>
+          <t>0-7</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1x2</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P12" t="inlineStr"/>
@@ -1496,12 +1496,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1x4</t>
+          <t>1-4</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P13" t="inlineStr"/>
@@ -1577,12 +1577,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2x1</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="P14" t="inlineStr"/>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>4x1</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P15" t="inlineStr"/>
@@ -1739,12 +1739,12 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P16" t="inlineStr"/>
@@ -1820,12 +1820,12 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P17" t="inlineStr"/>
@@ -1901,12 +1901,12 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P18" t="inlineStr"/>
@@ -1988,12 +1988,12 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0x1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P19" t="inlineStr"/>
@@ -2069,12 +2069,12 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>1x0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P20" t="inlineStr"/>
@@ -2150,12 +2150,12 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>3x0</t>
+          <t>3-0</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P21" t="inlineStr"/>
@@ -2231,12 +2231,12 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0x1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P22" t="inlineStr"/>
@@ -2312,12 +2312,12 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0x2</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P23" t="inlineStr"/>
@@ -2393,12 +2393,12 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0x1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P24" t="inlineStr"/>
@@ -2474,12 +2474,12 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>1x0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P25" t="inlineStr"/>
@@ -2555,12 +2555,12 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>4x1</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P26" t="inlineStr"/>
@@ -2636,12 +2636,12 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>3x0</t>
+          <t>3-0</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P27" t="inlineStr"/>
@@ -2717,12 +2717,12 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>0x1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P28" t="inlineStr"/>
@@ -2798,12 +2798,12 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>6x0</t>
+          <t>6-0</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P29" t="inlineStr"/>
@@ -2879,12 +2879,12 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>1x3</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P30" t="inlineStr"/>
@@ -2960,12 +2960,12 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P31" t="inlineStr"/>
@@ -3130,12 +3130,12 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P33" t="inlineStr"/>
@@ -3217,12 +3217,12 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2x1</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P34" t="inlineStr"/>
@@ -3377,12 +3377,12 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P36" t="inlineStr"/>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P37" t="inlineStr"/>
@@ -3539,12 +3539,12 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P38" t="inlineStr"/>
@@ -3620,12 +3620,12 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P39" t="inlineStr"/>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-13.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-13.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -605,12 +605,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>4-0</t>
+          <t>4x0</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
@@ -686,12 +686,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>3x1</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
@@ -767,12 +767,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>3x1</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
@@ -848,12 +848,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>3x1</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -929,12 +929,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>8-1</t>
+          <t>8x1</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>5-0</t>
+          <t>5x0</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -1091,12 +1091,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1x1</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -1172,12 +1172,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2-4</t>
+          <t>2x4</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -1253,12 +1253,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>0x0</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P10" t="inlineStr"/>
@@ -1334,12 +1334,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0-7</t>
+          <t>0x7</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>1x2</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P12" t="inlineStr"/>
@@ -1496,12 +1496,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1-4</t>
+          <t>1x4</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P13" t="inlineStr"/>
@@ -1577,12 +1577,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>2x1</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P14" t="inlineStr"/>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>4x1</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P15" t="inlineStr"/>
@@ -1739,12 +1739,12 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1x1</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P16" t="inlineStr"/>
@@ -1820,12 +1820,12 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1x1</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P17" t="inlineStr"/>
@@ -1901,12 +1901,12 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>vs</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P18" t="inlineStr"/>
@@ -1988,12 +1988,12 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0x1</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P19" t="inlineStr"/>
@@ -2069,12 +2069,12 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1x0</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P20" t="inlineStr"/>
@@ -2150,12 +2150,12 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>3-0</t>
+          <t>3x0</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P21" t="inlineStr"/>
@@ -2231,12 +2231,12 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0x1</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P22" t="inlineStr"/>
@@ -2312,12 +2312,12 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>0x2</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P23" t="inlineStr"/>
@@ -2393,12 +2393,12 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0x1</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P24" t="inlineStr"/>
@@ -2474,12 +2474,12 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1x0</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P25" t="inlineStr"/>
@@ -2555,12 +2555,12 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>4x1</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P26" t="inlineStr"/>
@@ -2636,12 +2636,12 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>3-0</t>
+          <t>3x0</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P27" t="inlineStr"/>
@@ -2717,12 +2717,12 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0x1</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P28" t="inlineStr"/>
@@ -2798,12 +2798,12 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>6-0</t>
+          <t>6x0</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P29" t="inlineStr"/>
@@ -2879,12 +2879,12 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>1x3</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P30" t="inlineStr"/>
@@ -2960,12 +2960,12 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1x1</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P31" t="inlineStr"/>
@@ -3130,12 +3130,12 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>vs</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P33" t="inlineStr"/>
@@ -3217,12 +3217,12 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>2x1</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P34" t="inlineStr"/>
@@ -3377,12 +3377,12 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1x1</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P36" t="inlineStr"/>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P37" t="inlineStr"/>
@@ -3539,12 +3539,12 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P38" t="inlineStr"/>
@@ -3620,12 +3620,12 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>vs</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P39" t="inlineStr"/>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-13.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-13.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1901,19 +1901,19 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>0x0</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="S18" t="n">
@@ -3130,19 +3130,19 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>1x1</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="S33" t="n">
@@ -3620,19 +3620,19 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>1x2</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="S39" t="inlineStr"/>
